--- a/docs/deliverables/프로젝트_명세서.xlsx
+++ b/docs/deliverables/프로젝트_명세서.xlsx
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>잔여 기능</t>
+          <t>세부 기능</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>acman-004~006</t>
+          <t>PATCH /users/{id}/password, /role</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1282,12 +1282,12 @@
       <c r="G22" s="3" t="inlineStr"/>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>미구현</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>보안 우선순위상 후순위</t>
+          <t>로컬 MySQL+Spring Boot 기동 후 curl로 권한별 성공/실패 케이스 검증</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>잔여 기능</t>
+          <t>세부 기능</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>stats-006</t>
+          <t>GET /regions/{id}/flows</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -1319,12 +1319,12 @@
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>설계 완료·구현 예정</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>집계 배치 로직 자체가 아직 없음</t>
+          <t>outflow_n/e/s/w + zone_neighbors로 집계, curl로 end-to-end 검증</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>설계 완료·구현 예정</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>별도 설계 문서 필요 — 현재 미착수</t>
+          <t>PATCH /users/{id}/password로 비밀번호 변경, PATCH /users/{id}/role로 SUPER_ADMIN이 USER↔ADMIN 권한 전환</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>미구현</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:I21"/>
+  <dimension ref="A2:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3496,6 +3496,147 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>FN-20</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>비밀번호 재설정</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>본인 비밀번호 변경 또는 관리자의 타인 비밀번호 초기화</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>userId, currentPassword(본인만), newPassword</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>본인 요청은 currentPassword 해시 일치 검증 후 변경, 관리자 요청은 검증 없이 바로 변경(초기화) — 관리자가 타인 비밀번호를 바꾸면 work_history 자동 기록</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>현재 비밀번호 불일치 403, 본인·관리자 아니면 403</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>acman-004</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>FN-21</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>관리자 간 관리(권한 전환)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN이 USER↔ADMIN 권한을 전환</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>userId, role(ADMIN/USER)</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN 전용으로 role 갱신, 대상이 SUPER_ADMIN 본인이거나 PRE_USER면 거부</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN 비관리자 403, 대상 부적격 409</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>acman-005~006</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>FN-22</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>구역 간 이동 조회</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>인접 구역 간 분단위 이동량 집계·조회</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>dongId, 기간(from~to)</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>zone_stats_minute의 outflow_n/e/s/w를 zone_neighbors(N/E/S/W)와 매칭해 zone_flows에 분단위 반영, 구간 합산 조회</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>구역명 포함 이동량 배열</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>인접 구역 미등록 시 해당 방향 집계 생략</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>stats-006</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3507,7 +3648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4805,17 +4946,17 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/users/{id}</t>
+          <t>/api/v1/users/{id}/password</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>회원 탈퇴</t>
+          <t>비밀번호 재설정</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -4825,7 +4966,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>path id</t>
+          <t>currentPassword(본인만), newPassword</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -4835,7 +4976,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>타인정보 403</t>
+          <t>현재 비밀번호 불일치 403</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4852,37 +4993,37 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>/api/v1/events?zoneId=&amp;status=</t>
+          <t>/api/v1/users/{id}/role</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>이벤트 목록 조회</t>
+          <t>권한 전환(USER↔ADMIN)</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>세션</t>
+          <t>세션(최고관리자)</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>zoneId, status(선택)</t>
+          <t>role(ADMIN/USER)</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>200 이벤트 배열</t>
+          <t>200 OK</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>비최고관리자 403, 대상 부적격 409</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
@@ -4899,22 +5040,22 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/events/{id}</t>
+          <t>/api/v1/users/{id}</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>이벤트 단건 조회</t>
+          <t>회원 탈퇴</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>세션</t>
+          <t>세션(본인/관리자)</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -4924,12 +5065,12 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>200 이벤트 상세</t>
+          <t>200 OK</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>타인정보 403</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -4946,37 +5087,37 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>/api/v1/events/{id}</t>
+          <t>/api/v1/events?zoneId=&amp;status=</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>이벤트 확인 · 조치완료</t>
+          <t>이벤트 목록 조회</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>세션(관리자)</t>
+          <t>세션</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>status, memo</t>
+          <t>zoneId, status(선택)</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>200 OK</t>
+          <t>200 이벤트 배열</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>일반회원 403</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
@@ -4998,32 +5139,32 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/history?adminId=&amp;actionType=</t>
+          <t>/api/v1/events/{id}</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>관리자 작업 이력 조회</t>
+          <t>이벤트 단건 조회</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>세션(최고관리자)</t>
+          <t>세션</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>adminId, actionType(선택)</t>
+          <t>path id</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>200 이력 배열</t>
+          <t>200 이벤트 상세</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>ADMIN도 403</t>
+          <t>404</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -5035,32 +5176,32 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>backend-api internal</t>
+          <t>backend-api 외부</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>/internal/v1/stats</t>
+          <t>/api/v1/events/{id}</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>초단위 통계 수신(analysis-server 전용)</t>
+          <t>이벤트 확인 · 조치완료</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>없음(내부망 가정)</t>
+          <t>세션(관리자)</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>cameraId, at, personCount, in/out, dwellSec, avgSpeedPxS, moves</t>
+          <t>status, memo</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
@@ -5070,7 +5211,7 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>구역매핑 없음 시 무시</t>
+          <t>일반회원 403</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
@@ -5082,42 +5223,42 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>backend-api internal</t>
+          <t>backend-api 외부</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>/internal/v1/cameras/{id}/status</t>
+          <t>/api/v1/history?adminId=&amp;actionType=</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>분석 상태 · 진행률 보고</t>
+          <t>관리자 작업 이력 조회</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>없음(내부망 가정)</t>
+          <t>세션(최고관리자)</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>status, progress, errorMessage</t>
+          <t>adminId, actionType(선택)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>200 OK</t>
+          <t>200 이력 배열</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ADMIN도 403</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -5129,7 +5270,7 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>analysis-server</t>
+          <t>backend-api internal</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
@@ -5139,32 +5280,32 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>/analyzer/v1/cameras</t>
+          <t>/internal/v1/stats</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>분석 시작</t>
+          <t>초단위 통계 수신(analysis-server 전용)</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>없음(내부망 가정)</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>cameraId, sourceType, sourceUri</t>
+          <t>cameraId, at, personCount, in/out, dwellSec, avgSpeedPxS, moves</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>202 Accepted</t>
+          <t>200 OK</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>구역매핑 없음 시 무시</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
@@ -5176,32 +5317,32 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>analysis-server</t>
+          <t>backend-api internal</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>/analyzer/v1/cameras/{cameraId}</t>
+          <t>/internal/v1/cameras/{id}/status</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>분석 정지</t>
+          <t>분석 상태 · 진행률 보고</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>없음(내부망 가정)</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>path cameraId</t>
+          <t>status, progress, errorMessage</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -5228,17 +5369,17 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>/analyzer/v1/cameras/{cameraId}/live</t>
+          <t>/analyzer/v1/cameras</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>라이브뷰(박스 포함 MJPEG)</t>
+          <t>분석 시작</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
@@ -5248,17 +5389,17 @@
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>path cameraId</t>
+          <t>cameraId, sourceType, sourceUri</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>200 multipart/x-mixed-replace</t>
+          <t>202 Accepted</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>캐시 없으면 빈 스트림</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
@@ -5275,17 +5416,17 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>/analyzer/v1/health</t>
+          <t>/analyzer/v1/cameras/{cameraId}</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>헬스체크</t>
+          <t>분석 정지</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -5295,7 +5436,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>path cameraId</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -5317,7 +5458,7 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>backend-api 외부</t>
+          <t>analysis-server</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
@@ -5327,32 +5468,32 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>/api/v1/zones/{id}/stats/export?from=&amp;to=</t>
+          <t>/analyzer/v1/cameras/{cameraId}/live</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>통계 엑셀 다운로드</t>
+          <t>라이브뷰(박스 포함 MJPEG)</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>세션</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>path id, from, to(ISO)</t>
+          <t>path cameraId</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>200 xlsx 파일 다운로드</t>
+          <t>200 multipart/x-mixed-replace</t>
         </is>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>캐시 없으면 빈 스트림</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
@@ -5364,7 +5505,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>backend-api 외부</t>
+          <t>analysis-server</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -5374,27 +5515,27 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/zones/{id}/stats/stream</t>
+          <t>/analyzer/v1/health</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>실시간 통계 스트림(SSE)</t>
+          <t>헬스체크</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>세션</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>path id</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>200 text/event-stream('stat' 이벤트)</t>
+          <t>200 OK</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -5421,12 +5562,12 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>/api/v1/zones/{id}/playback?from=&amp;to=</t>
+          <t>/api/v1/zones/{id}/stats/export?from=&amp;to=</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>녹화 이력 + 통계 타임라인 조회</t>
+          <t>통계 엑셀 다운로드</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
@@ -5441,7 +5582,7 @@
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>200 {recordings, timeline} JSON</t>
+          <t>200 xlsx 파일 다운로드</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
@@ -5458,7 +5599,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>backend-api 외부(예정)</t>
+          <t>backend-api 외부</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -5468,37 +5609,131 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/regions/{id}/flows</t>
+          <t>/api/v1/zones/{id}/stats/stream</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
+          <t>실시간 통계 스트림(SSE)</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>세션</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>path id</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>200 text/event-stream('stat' 이벤트)</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>backend-api 외부</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>/api/v1/zones/{id}/playback?from=&amp;to=</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>녹화 이력 + 통계 타임라인 조회</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>세션</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>path id, from, to(ISO)</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>200 {recordings, timeline} JSON</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>backend-api 외부</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/regions/{id}/flows?from=&amp;to=</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
           <t>구역 간 이동 조회</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>세션</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>from, to</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>200 이동량 배열</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>설계 완료·구현 예정</t>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>path id(동 레벨), from, to(ISO)</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>200 구역명 포함 이동량 배열</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6558,6 +6793,120 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TC-25</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>비밀번호 재설정 권한별 검증</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>본인(현재 비밀번호 틀림/맞음), 관리자의 타인 초기화, 제3자의 무단 변경 시도</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>본인·관리자만 성공, 현재 비밀번호 틀리면 실패, 제3자는 차단</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>현재 비밀번호 틀림 403, 맞으면 200(재로그인 확인), 관리자 초기화 200(재로그인 확인), 제3자 시도 403 전부 확인</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>backend-api</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>TC-26</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>관리자 간 관리(권한 전환) 검증</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>USER→ADMIN 승격, ADMIN→USER 강등, SUPER_ADMIN 본인 대상, 비관리자의 호출</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>승격·강등은 성공, SUPER_ADMIN 본인은 409, 비관리자는 403</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>승격 200, 강등 200, SUPER_ADMIN 본인 변경 시도 409, 일반회원 호출 403 전부 확인, work_history 기록도 확인</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>backend-api</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TC-27</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>구역 간 이동 조회 집계 검증</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>인접 구역(N) 등록 후 outflow_n=7인 샘플 전송, GET /regions/{id}/flows 조회</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>zone_flows에 from→to(N 방향 인접 구역) count=7 반영, API 응답 일치</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>zone_stats_minute outflow_n=7 확인 → zone_flows에 동일 count로 적재 확인 → API 응답의 구역명·count가 DB와 일치함을 확인</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>backend-api</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
